--- a/3_Automation_Dashboard/audit/งบการเงิน_2026.xlsx
+++ b/3_Automation_Dashboard/audit/งบการเงิน_2026.xlsx
@@ -747,13 +747,13 @@
         <v/>
       </c>
       <c r="F9">
-        <v>12023</v>
+        <v>4500</v>
       </c>
       <c r="G9">
-        <v>5800</v>
+        <v>6700</v>
       </c>
       <c r="H9">
-        <v>21200</v>
+        <v>24200</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -870,7 +870,7 @@
         <v>2160</v>
       </c>
       <c r="F12">
-        <v>1122</v>
+        <v>1907</v>
       </c>
       <c r="G12">
         <v>6460</v>
@@ -1485,13 +1485,13 @@
         <v>267605</v>
       </c>
       <c r="F27">
-        <v>207137</v>
+        <v>200399</v>
       </c>
       <c r="G27">
-        <v>190167</v>
+        <v>191067</v>
       </c>
       <c r="H27">
-        <v>259349</v>
+        <v>262349</v>
       </c>
       <c r="I27" t="str">
         <v/>
@@ -1772,7 +1772,7 @@
         <v>4000</v>
       </c>
       <c r="F35">
-        <v>6785</v>
+        <v>11504</v>
       </c>
       <c r="G35">
         <v>2419</v>
@@ -1813,7 +1813,7 @@
         <v>125016</v>
       </c>
       <c r="F36">
-        <v>90785</v>
+        <v>95504</v>
       </c>
       <c r="G36">
         <v>85819</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F39">
-        <v>1065</v>
+        <v>3084</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1936,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="F40">
-        <v>1065</v>
+        <v>3084</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -1980,10 +1980,10 @@
         <v>298987</v>
       </c>
       <c r="G42">
-        <v>275986</v>
+        <v>276886</v>
       </c>
       <c r="H42">
-        <v>354768.75</v>
+        <v>357768.75</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -2059,13 +2059,13 @@
         <v>46253</v>
       </c>
       <c r="F45">
-        <v>48643</v>
+        <v>55381</v>
       </c>
       <c r="G45">
-        <v>1553</v>
+        <v>653</v>
       </c>
       <c r="H45">
-        <v>-17259</v>
+        <v>-20259</v>
       </c>
       <c r="I45" t="str">
         <v/>
@@ -2100,13 +2100,13 @@
         <v>-78763</v>
       </c>
       <c r="F46">
-        <v>-42142</v>
+        <v>-40123</v>
       </c>
       <c r="G46">
-        <v>-84266</v>
+        <v>-85166</v>
       </c>
       <c r="H46">
-        <v>-112678.75</v>
+        <v>-115678.75</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -2144,10 +2144,10 @@
         <v>-43207</v>
       </c>
       <c r="G47">
-        <v>-84266</v>
+        <v>-85166</v>
       </c>
       <c r="H47">
-        <v>-112678.75</v>
+        <v>-115678.75</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -2223,13 +2223,13 @@
         <v>0.14736919243734428</v>
       </c>
       <c r="F50">
-        <v>0.1901751505199781</v>
+        <v>0.21651810149347095</v>
       </c>
       <c r="G50">
-        <v>0.00810035468391404</v>
+        <v>0.003406008762779053</v>
       </c>
       <c r="H50">
-        <v>-0.07129166838778966</v>
+        <v>-0.08368375397579413</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -2264,13 +2264,13 @@
         <v>-0.2509510670430577</v>
       </c>
       <c r="F51">
-        <v>-0.164758777074048</v>
+        <v>-0.15686527484557042</v>
       </c>
       <c r="G51">
-        <v>-0.4395263926559566</v>
+        <v>-0.4442207385770916</v>
       </c>
       <c r="H51">
-        <v>-0.4654415713164526</v>
+        <v>-0.477833656904457</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -2308,10 +2308,10 @@
         <v>-0.16892251153334897</v>
       </c>
       <c r="G52">
-        <v>-0.4395263926559566</v>
+        <v>-0.4442207385770916</v>
       </c>
       <c r="H52">
-        <v>-0.4654415713164526</v>
+        <v>-0.477833656904457</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -4552,13 +4552,13 @@
         <v/>
       </c>
       <c r="F9">
-        <v>12023</v>
+        <v>4500</v>
       </c>
       <c r="G9">
-        <v>5800</v>
+        <v>6700</v>
       </c>
       <c r="H9">
-        <v>21200</v>
+        <v>24200</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -4675,7 +4675,7 @@
         <v>2160</v>
       </c>
       <c r="F12">
-        <v>1122</v>
+        <v>1907</v>
       </c>
       <c r="G12">
         <v>6460</v>
@@ -5290,13 +5290,13 @@
         <v>269657</v>
       </c>
       <c r="F27">
-        <v>211967</v>
+        <v>205229</v>
       </c>
       <c r="G27">
-        <v>190167</v>
+        <v>191067</v>
       </c>
       <c r="H27">
-        <v>259349</v>
+        <v>262349</v>
       </c>
       <c r="I27" t="str">
         <v/>
@@ -5618,7 +5618,7 @@
         <v>4000</v>
       </c>
       <c r="F35">
-        <v>6785</v>
+        <v>11504</v>
       </c>
       <c r="G35">
         <v>2419</v>
@@ -5659,7 +5659,7 @@
         <v>173016</v>
       </c>
       <c r="F36">
-        <v>143985</v>
+        <v>148704</v>
       </c>
       <c r="G36">
         <v>146219</v>
@@ -5782,7 +5782,7 @@
         <v/>
       </c>
       <c r="F39">
-        <v>1065</v>
+        <v>3084</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -5823,7 +5823,7 @@
         <v>0</v>
       </c>
       <c r="F40">
-        <v>1065</v>
+        <v>3084</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -5908,10 +5908,10 @@
         <v>357017</v>
       </c>
       <c r="G42">
-        <v>336386</v>
+        <v>337286</v>
       </c>
       <c r="H42">
-        <v>483268.75</v>
+        <v>486268.75</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -6028,13 +6028,13 @@
         <v>113461</v>
       </c>
       <c r="F45">
-        <v>215344</v>
+        <v>222082</v>
       </c>
       <c r="G45">
-        <v>117323</v>
+        <v>116423</v>
       </c>
       <c r="H45">
-        <v>290598</v>
+        <v>287598</v>
       </c>
       <c r="I45" t="str">
         <v/>
@@ -6069,13 +6069,13 @@
         <v>-59555</v>
       </c>
       <c r="F46">
-        <v>71359</v>
+        <v>73378</v>
       </c>
       <c r="G46">
-        <v>-28896</v>
+        <v>-29796</v>
       </c>
       <c r="H46">
-        <v>66678.25</v>
+        <v>63678.25</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -6113,10 +6113,10 @@
         <v>70294</v>
       </c>
       <c r="G47">
-        <v>-28896</v>
+        <v>-29796</v>
       </c>
       <c r="H47">
-        <v>66678.25</v>
+        <v>63678.25</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -6233,13 +6233,13 @@
         <v>0.2961515773208254</v>
       </c>
       <c r="F50">
-        <v>0.5039514545611978</v>
+        <v>0.519719829351456</v>
       </c>
       <c r="G50">
-        <v>0.38155061953234254</v>
+        <v>0.37862369507951477</v>
       </c>
       <c r="H50">
-        <v>0.5284109195977067</v>
+        <v>0.522955848472671</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -6274,13 +6274,13 @@
         <v>-0.15544819089679943</v>
       </c>
       <c r="F51">
-        <v>0.16699546700178558</v>
+        <v>0.17172036292068307</v>
       </c>
       <c r="G51">
-        <v>-0.09397378776545579</v>
+        <v>-0.09690071221828352</v>
       </c>
       <c r="H51">
-        <v>0.12124486541430356</v>
+        <v>0.11578979428926787</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -6318,10 +6318,10 @@
         <v>0.1645031370594251</v>
       </c>
       <c r="G52">
-        <v>-0.09397378776545579</v>
+        <v>-0.09690071221828352</v>
       </c>
       <c r="H52">
-        <v>0.12124486541430356</v>
+        <v>0.11578979428926787</v>
       </c>
       <c r="I52" t="str">
         <v/>
